--- a/AAII_Financials/Yearly/FRTAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FRTAY_YR_FIN.xlsx
@@ -714,25 +714,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2895400</v>
+        <v>2864700</v>
       </c>
       <c r="E8" s="3">
-        <v>2590400</v>
+        <v>2565000</v>
       </c>
       <c r="F8" s="3">
-        <v>2663600</v>
+        <v>2636600</v>
       </c>
       <c r="G8" s="3">
-        <v>2759100</v>
+        <v>2732400</v>
       </c>
       <c r="H8" s="3">
-        <v>2933200</v>
+        <v>2907200</v>
       </c>
       <c r="I8" s="3">
-        <v>3178400</v>
+        <v>3151400</v>
       </c>
       <c r="J8" s="3">
-        <v>3313700</v>
+        <v>3290900</v>
       </c>
       <c r="K8" s="3">
         <v>3338200</v>
@@ -780,25 +780,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>911900</v>
+        <v>881300</v>
       </c>
       <c r="E10" s="3">
-        <v>801000</v>
+        <v>775500</v>
       </c>
       <c r="F10" s="3">
-        <v>793900</v>
+        <v>766800</v>
       </c>
       <c r="G10" s="3">
-        <v>727600</v>
+        <v>700900</v>
       </c>
       <c r="H10" s="3">
-        <v>742900</v>
+        <v>716900</v>
       </c>
       <c r="I10" s="3">
-        <v>799100</v>
+        <v>772100</v>
       </c>
       <c r="J10" s="3">
-        <v>761200</v>
+        <v>738500</v>
       </c>
       <c r="K10" s="3">
         <v>802000</v>
@@ -972,25 +972,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2436800</v>
+        <v>2406100</v>
       </c>
       <c r="E17" s="3">
-        <v>2189700</v>
+        <v>2164200</v>
       </c>
       <c r="F17" s="3">
-        <v>2378800</v>
+        <v>2351700</v>
       </c>
       <c r="G17" s="3">
-        <v>2621000</v>
+        <v>2594300</v>
       </c>
       <c r="H17" s="3">
-        <v>2604300</v>
+        <v>2578300</v>
       </c>
       <c r="I17" s="3">
-        <v>2857500</v>
+        <v>2830400</v>
       </c>
       <c r="J17" s="3">
-        <v>3012700</v>
+        <v>2989900</v>
       </c>
       <c r="K17" s="3">
         <v>3012200</v>
